--- a/output/pdf_financials_xlsx/AG.xlsx
+++ b/output/pdf_financials_xlsx/AG.xlsx
@@ -2407,25 +2407,25 @@
         <v>3.504065</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>10.109</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>15.44</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>25.405</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>115.658</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>154.843</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>75.039</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>79.593</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>65.584</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>54.405</v>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
@@ -2480,25 +2480,25 @@
         <v>6.584098</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>42.75</v>
+        <v>52.859</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>137.537</v>
+        <v>152.977</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>110.989</v>
+        <v>136.394</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>26.193</v>
+        <v>141.851</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-80.937</v>
+        <v>73.90600000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-126.252</v>
+        <v>-51.213</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>25.491</v>
+        <v>105.084</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         <v>-202.016</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-39.024</v>
+        <v>26.56</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>29.729</v>
+        <v>84.134</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
         <v>11.06372707724055</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>61.26133872146511</v>
+        <v>75.74767493515613</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>56.02002329806039</v>
+        <v>62.3088703699178</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>44.90264061785684</v>
+        <v>55.18070046970389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.30854004644134</v>
+        <v>104.5674689469611</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-32.971854338359</v>
+        <v>30.10758820725701</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-57.53267348389567</v>
+        <v>-23.33761688631268</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.166885431013712</v>
+        <v>37.7895331149286</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-10.72252874068538</v>
+        <v>7.297826039170861</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.17009091009025</v>
+        <v>23.12161285712715</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -2789,10 +2789,10 @@
         <v>91.184</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>111.591</v>
+        <v>108.419</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>54.765</v>
+        <v>45.307</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>40.345</v>
@@ -2801,10 +2801,10 @@
         <v>51.018</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>129.049</v>
+        <v>91.498</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>118.141</v>
+        <v>77.411</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>91.184</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>116.835</v>
+        <v>113.663</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>54.788</v>
+        <v>45.33</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>40.345</v>
@@ -2927,10 +2927,10 @@
         <v>51.018</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>166.6</v>
+        <v>129.049</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>158.871</v>
+        <v>118.141</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>2.174848</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>15.593</v>
@@ -2981,7 +2981,7 @@
         <v>19.598</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>22.045</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>13.561</v>
@@ -3161,19 +3161,19 @@
         <v>6.725989</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>8.513999999999999</v>
+        <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>8.353999999999999</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>19.598</v>
+        <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>22.045</v>
+        <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>13.561</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
@@ -3227,16 +3227,16 @@
         <v>8.513999999999999</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>23.947</v>
+        <v>15.593</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>39.196</v>
+        <v>19.598</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>22.045</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>27.122</v>
+        <v>13.561</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>24.491</v>
@@ -3668,25 +3668,25 @@
         <v>4.863</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.78</v>
+        <v>16.134</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>16.015</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>32.7</v>
+        <v>42.158</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>3.797</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>7.072</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>14.423</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>11.787</v>
+        <v>52.517</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>15.735</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>25.98</v>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>75.822</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>80.352</v>
       </c>
       <c r="K100" s="1" t="inlineStr">
         <is>
@@ -7004,25 +7004,25 @@
         </is>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>67.22</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>56.283</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>118.283</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>137.411</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>126.17</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>125.492</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>264.798</v>
       </c>
     </row>
     <row r="101">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -31196,7 +31196,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -32044,7 +32044,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -36468,7 +36468,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -40786,7 +40786,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -43970,7 +43970,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -52654,7 +52654,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -71696,7 +71696,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -77978,7 +77978,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -78194,7 +78194,7 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -80102,7 +80102,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -83150,7 +83150,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -85440,7 +85440,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
